--- a/out/Attention-MambaAMT_repeat_1_000007.xlsx
+++ b/out/Attention-MambaAMT_repeat_1_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.134689842160187</v>
+        <v>3.228705708809411</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-2.134689842160187</v>
+        <v>3.228705708809411</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-2.134689842160187</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.7683004144223875</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.134689842160187</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.134689842160187</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.134689842160187</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.7683004144223875</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.2554444171274072</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.534689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.534689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.534689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-2.134689842160187</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.2554444171274072</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.2554444171274072</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.368300414422388</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.368300414422388</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.534689842160187</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.368300414422388</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002043440127101494</v>
+        <v>-0.000391969883532729</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.355784594133036</v>
+        <v>4.518833854729427</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.368300414422388</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC40" t="n">
-        <v>4.715210957658555</v>
+        <v>9.044653011089986</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.3532604312070811</v>
+        <v>0.6776192940205544</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.368300414422388</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC41" t="n">
-        <v>3.062785287458138</v>
+        <v>5.874992847803057</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.4416904825196963</v>
+        <v>0.8472445438445323</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.368300414422388</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC42" t="n">
-        <v>3.592961921510522</v>
+        <v>6.891970365717502</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.6331610493433873</v>
+        <v>1.214521198302129</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.368300414422388</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC43" t="n">
-        <v>4.417843128770547</v>
+        <v>8.474246242655786</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.6773572544527504</v>
+        <v>1.299297110085373</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC44" t="n">
-        <v>5.13944347035679</v>
+        <v>9.85840981704181</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.7178614242953602</v>
+        <v>1.376992313482098</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC45" t="n">
-        <v>5.89786179672264</v>
+        <v>11.31319712833096</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.3239581753043008</v>
+        <v>0.6214110207047058</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC46" t="n">
-        <v>5.827318706324929</v>
+        <v>11.17788243713265</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1564569916642515</v>
+        <v>0.3001137636143597</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC47" t="n">
-        <v>5.816020486872905</v>
+        <v>11.15621033973502</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.07454648561131087</v>
+        <v>0.142994660511181</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC48" t="n">
-        <v>5.808533444610631</v>
+        <v>11.14184879192911</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02208796688338367</v>
+        <v>0.04236868364818479</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC49" t="n">
-        <v>5.778082259577305</v>
+        <v>11.08343795528665</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01460981607301913</v>
+        <v>0.02802530428311959</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC50" t="n">
-        <v>5.785202942153425</v>
+        <v>11.09709775777395</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.007475026802741177</v>
+        <v>0.01434303352243776</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC51" t="n">
-        <v>5.785534487774508</v>
+        <v>11.09773831266038</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.003821322784486395</v>
+        <v>0.007334573644222652</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC52" t="n">
-        <v>5.785697656889356</v>
+        <v>11.09805589119665</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001433081342647674</v>
+        <v>0.002753845523131985</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC53" t="n">
-        <v>5.784740355289936</v>
+        <v>11.09622420543614</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0007787556783956723</v>
+        <v>0.001498985896542432</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC54" t="n">
-        <v>5.784864052392041</v>
+        <v>11.09646603752376</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.000372496726515206</v>
+        <v>0.0007189989849586371</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC55" t="n">
-        <v>5.784829764267422</v>
+        <v>11.0964048938073</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0002291813179495396</v>
+        <v>0.0004436835335503784</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC56" t="n">
-        <v>5.784914658553841</v>
+        <v>11.09657212823842</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001174949297407688</v>
+        <v>0.000229696167906683</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC57" t="n">
-        <v>5.784920331034145</v>
+        <v>11.09658757635195</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>5.394649471632548e-05</v>
+        <v>0.0001088966169095103</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC58" t="n">
-        <v>5.784911652107194</v>
+        <v>11.09657552648654</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.337439133288135e-05</v>
+        <v>6.791134353247457e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC59" t="n">
-        <v>5.784923428912399</v>
+        <v>11.09660240241643</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.248416916455026e-05</v>
+        <v>2.763711577382715e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC60" t="n">
-        <v>5.784914997524471</v>
+        <v>11.09659088348747</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>2.205584102398162e-06</v>
+        <v>9.411168204796322e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC61" t="n">
-        <v>5.784907942669891</v>
+        <v>11.09658191018411</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-5.494870763551826e-07</v>
+        <v>2.788397616378431e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC62" t="n">
-        <v>5.784903604132617</v>
+        <v>11.09657815110299</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-3.062365791830193e-06</v>
+        <v>-1.124731583660385e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC63" t="n">
-        <v>5.784898025837493</v>
+        <v>11.09657199451274</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.053889915940302e-06</v>
+        <v>-3.107779831880603e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC64" t="n">
-        <v>5.784892979216425</v>
+        <v>11.0965669012706</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>-3.735991635587426e-06</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC65" t="n">
-        <v>5.784893297496642</v>
+        <v>11.09656253629664</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC66" t="n">
-        <v>5.784894388743099</v>
+        <v>11.09656362754309</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC67" t="n">
-        <v>5.784893699135963</v>
+        <v>11.09656293793596</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC68" t="n">
-        <v>5.784893729448365</v>
+        <v>11.09656296824836</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC69" t="n">
-        <v>5.784893539995855</v>
+        <v>11.09656277879585</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC70" t="n">
-        <v>5.784893593042558</v>
+        <v>11.09656283184255</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC71" t="n">
-        <v>5.784893646089261</v>
+        <v>11.09656288488925</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC72" t="n">
-        <v>5.784893608198758</v>
+        <v>11.09656284699875</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC73" t="n">
-        <v>5.784893479371052</v>
+        <v>11.09656271817104</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC74" t="n">
-        <v>5.784893335387144</v>
+        <v>11.09656257418714</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC75" t="n">
-        <v>5.784893176247036</v>
+        <v>11.09656241504703</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC76" t="n">
-        <v>5.784893229293738</v>
+        <v>11.09656246809373</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC77" t="n">
-        <v>5.784893176247036</v>
+        <v>11.09656241504703</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC78" t="n">
-        <v>5.784893176247036</v>
+        <v>11.09656241504703</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC79" t="n">
-        <v>5.784892994372627</v>
+        <v>11.09656223317262</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC80" t="n">
-        <v>5.784893161090835</v>
+        <v>11.09656239989083</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC81" t="n">
-        <v>5.784893358121446</v>
+        <v>11.09656259692144</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC82" t="n">
-        <v>5.784893198981337</v>
+        <v>11.09656243778133</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC83" t="n">
-        <v>5.784893236871839</v>
+        <v>11.09656247567183</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC84" t="n">
-        <v>5.784893433902449</v>
+        <v>11.09656267270244</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC85" t="n">
-        <v>5.784893411168148</v>
+        <v>11.09656264996814</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC86" t="n">
-        <v>5.78489325960614</v>
+        <v>11.09656249840613</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC87" t="n">
-        <v>5.784893183825136</v>
+        <v>11.09656242262513</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC88" t="n">
-        <v>5.784893282340442</v>
+        <v>11.09656252114043</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC89" t="n">
-        <v>5.784893289918542</v>
+        <v>11.09656252871853</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC90" t="n">
-        <v>5.784893555152056</v>
+        <v>11.09656279395205</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC91" t="n">
-        <v>5.78489325960614</v>
+        <v>11.09656249840613</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC92" t="n">
-        <v>5.784893502105352</v>
+        <v>11.09656274090535</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC93" t="n">
-        <v>5.784893585464457</v>
+        <v>11.09656282426445</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC94" t="n">
-        <v>5.784893418746249</v>
+        <v>11.09656265754624</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC95" t="n">
-        <v>5.784893608198758</v>
+        <v>11.09656284699875</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC96" t="n">
-        <v>5.78489325960614</v>
+        <v>11.09656249840613</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC97" t="n">
-        <v>5.784893054997429</v>
+        <v>11.09656229379742</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC98" t="n">
-        <v>5.784893168668935</v>
+        <v>11.09656240746893</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC99" t="n">
-        <v>5.784893183825136</v>
+        <v>11.09656242262513</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC100" t="n">
-        <v>5.784892948904025</v>
+        <v>11.09656218770402</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC101" t="n">
-        <v>5.784893009528827</v>
+        <v>11.09656224832882</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC102" t="n">
-        <v>5.78489288070112</v>
+        <v>11.09656211950111</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC103" t="n">
-        <v>5.784893017106928</v>
+        <v>11.09656225590692</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC104" t="n">
-        <v>5.784893191403237</v>
+        <v>11.09656243020323</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC105" t="n">
-        <v>5.784893335387144</v>
+        <v>11.09656257418714</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC106" t="n">
-        <v>5.784893168668935</v>
+        <v>11.09656240746893</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC107" t="n">
-        <v>5.784893161090835</v>
+        <v>11.09656239989083</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC108" t="n">
-        <v>5.78489287312302</v>
+        <v>11.09656211192301</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC109" t="n">
-        <v>5.784892888279221</v>
+        <v>11.09656212707921</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC110" t="n">
-        <v>5.784893115622233</v>
+        <v>11.09656235442223</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC111" t="n">
-        <v>5.784893100466031</v>
+        <v>11.09656233926602</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC112" t="n">
-        <v>5.784893206559437</v>
+        <v>11.09656244535943</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC113" t="n">
-        <v>5.784892933747823</v>
+        <v>11.09656217254781</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC114" t="n">
-        <v>5.784893032263128</v>
+        <v>11.09656227106312</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC115" t="n">
-        <v>5.784893183825136</v>
+        <v>11.09656242262513</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC116" t="n">
-        <v>5.784893198981337</v>
+        <v>11.09656243778133</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC117" t="n">
-        <v>5.784893176247036</v>
+        <v>11.09656241504703</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC118" t="n">
-        <v>5.78489325960614</v>
+        <v>11.09656249840613</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC119" t="n">
-        <v>5.784893358121446</v>
+        <v>11.09656259692144</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC120" t="n">
-        <v>5.784893191403237</v>
+        <v>11.09656243020323</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC121" t="n">
-        <v>5.784893176247036</v>
+        <v>11.09656241504703</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC122" t="n">
-        <v>5.784893145934634</v>
+        <v>11.09656238473463</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC123" t="n">
-        <v>5.784893130778434</v>
+        <v>11.09656236957843</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC124" t="n">
-        <v>5.784893168668935</v>
+        <v>11.09656240746893</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC125" t="n">
-        <v>5.784893183825136</v>
+        <v>11.09656242262513</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC126" t="n">
-        <v>5.784893176247036</v>
+        <v>11.09656241504703</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_1_000007.xlsx
+++ b/out/Attention-MambaAMT_repeat_1_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.134689842160187</v>
+        <v>-1.298073034624129</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-2.134689842160187</v>
+        <v>-1.298073034624129</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.6345324045481114</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.6345324045481114</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.6345324045481114</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.134689842160187</v>
+        <v>-1.298073034624129</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.6345324045481114</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.6345324045481114</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.6345324045481114</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.534689842160187</v>
+        <v>-1.098073034624129</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-2.134689842160187</v>
+        <v>-1.298073034624129</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-2.134689842160187</v>
+        <v>-1.298073034624129</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-2.134689842160187</v>
+        <v>-1.298073034624129</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-2.134689842160187</v>
+        <v>-1.298073034624129</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.134689842160187</v>
+        <v>-1.298073034624129</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.134689842160187</v>
+        <v>-1.298073034624129</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.134689842160187</v>
+        <v>-1.298073034624129</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-2.134689842160187</v>
+        <v>-1.298073034624129</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-2.134689842160187</v>
+        <v>-1.298073034624129</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-2.134689842160187</v>
+        <v>-1.298073034624129</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.4345324045481114</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.368300414422388</v>
+        <v>-0.4345324045481114</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.534689842160187</v>
+        <v>-0.4345324045481114</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.534689842160187</v>
+        <v>-1.098073034624129</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-2.134689842160187</v>
+        <v>-1.098073034624129</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-2.134689842160187</v>
+        <v>-1.298073034624129</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-2.134689842160187</v>
+        <v>-1.298073034624129</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-2.134689842160187</v>
+        <v>-1.298073034624129</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-2.134689842160187</v>
+        <v>-1.298073034624129</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-2.134689842160187</v>
+        <v>-1.298073034624129</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-2.134689842160187</v>
+        <v>-1.298073034624129</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-2.134689842160187</v>
+        <v>-1.298073034624129</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-2.134689842160187</v>
+        <v>-1.298073034624129</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.4345324045481114</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.368300414422388</v>
+        <v>0.2290082255279058</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.368300414422388</v>
+        <v>0.2290082255279058</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.534689842160187</v>
+        <v>0.2290082255279058</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.368300414422388</v>
+        <v>0.2290082255279058</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002043440127101494</v>
+        <v>-0.000117463736568694</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.355784594133036</v>
+        <v>1.354183399820833</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC40" t="n">
-        <v>4.715210957658555</v>
+        <v>2.710460122790009</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.3532604312070811</v>
+        <v>0.2030658415114248</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC41" t="n">
-        <v>3.062785287458138</v>
+        <v>1.760590905601549</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.4416904825196963</v>
+        <v>0.2538983185004479</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC42" t="n">
-        <v>3.592961921510522</v>
+        <v>2.065354062939217</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.6331610493433873</v>
+        <v>0.3639620354825855</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC43" t="n">
-        <v>4.417843128770547</v>
+        <v>2.539523313649628</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.6773572544527504</v>
+        <v>0.389367632504495</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC44" t="n">
-        <v>5.13944347035679</v>
+        <v>2.954323354205582</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.7178614242953602</v>
+        <v>0.4126512097736045</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC45" t="n">
-        <v>5.89786179672264</v>
+        <v>3.390287604693023</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.3239581753043008</v>
+        <v>0.1862218161639586</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.368300414422388</v>
+        <v>0.2290082255279058</v>
       </c>
       <c r="JC46" t="n">
-        <v>5.827318706324929</v>
+        <v>3.349737115731476</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1564569916642515</v>
+        <v>0.08993598248957481</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-2.134689842160187</v>
+        <v>0.02900822552790579</v>
       </c>
       <c r="JC47" t="n">
-        <v>5.816020486872905</v>
+        <v>3.343242528497804</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.07454648561131087</v>
+        <v>0.04285243098718765</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.7683004144223875</v>
+        <v>-0.6345324045481114</v>
       </c>
       <c r="JC48" t="n">
-        <v>5.808533444610631</v>
+        <v>3.338938698997445</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02208796688338367</v>
+        <v>0.01269539679674733</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-2.134689842160187</v>
+        <v>0.02900822552790581</v>
       </c>
       <c r="JC49" t="n">
-        <v>5.778082259577305</v>
+        <v>3.321433259006042</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01460981607301913</v>
+        <v>0.008396308371361957</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.02900822552790581</v>
       </c>
       <c r="JC50" t="n">
-        <v>5.785202942153425</v>
+        <v>3.325524448542696</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.007475026802741177</v>
+        <v>0.004294883863191126</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.692548855603923</v>
       </c>
       <c r="JC51" t="n">
-        <v>5.785534487774508</v>
+        <v>3.325712911363552</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.003821322784486395</v>
+        <v>0.002194556770350637</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.368300414422388</v>
+        <v>0.2290082255279059</v>
       </c>
       <c r="JC52" t="n">
-        <v>5.785697656889356</v>
+        <v>3.325804583164641</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001433081342647674</v>
+        <v>0.000821518329563821</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-2.134689842160187</v>
+        <v>0.229008225527906</v>
       </c>
       <c r="JC53" t="n">
-        <v>5.784740355289936</v>
+        <v>3.32525215400199</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0007787556783956723</v>
+        <v>0.0004454532635831969</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.0290082255279059</v>
       </c>
       <c r="JC54" t="n">
-        <v>5.784864052392041</v>
+        <v>3.325321149972224</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.000372496726515206</v>
+        <v>0.0002119612765024237</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC55" t="n">
-        <v>5.784829764267422</v>
+        <v>3.325299304117223</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0002291813179495396</v>
+        <v>0.0001298018510886005</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC56" t="n">
-        <v>5.784914658553841</v>
+        <v>3.325346049987977</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001174949297407688</v>
+        <v>6.49971027090107e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC57" t="n">
-        <v>5.784920331034145</v>
+        <v>3.325347194016753</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>5.394649471632548e-05</v>
+        <v>2.896916644669604e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC58" t="n">
-        <v>5.784911652107194</v>
+        <v>3.325340061112915</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.337439133288135e-05</v>
+        <v>1.67454884219661e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.368300414422388</v>
+        <v>0.2290082255279059</v>
       </c>
       <c r="JC59" t="n">
-        <v>5.784923428912399</v>
+        <v>3.325344848358913</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.248416916455026e-05</v>
+        <v>5.490501498730158e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.6345324045481114</v>
       </c>
       <c r="JC60" t="n">
-        <v>5.784914997524471</v>
+        <v>3.325337789526157</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>2.205584102398162e-06</v>
+        <v>-8.825233700581938e-07</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.6345324045481114</v>
       </c>
       <c r="JC61" t="n">
-        <v>5.784907942669891</v>
+        <v>3.325331556863908</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-5.494870763551826e-07</v>
+        <v>-2.77474353817759e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.02900822552790579</v>
       </c>
       <c r="JC62" t="n">
-        <v>5.784903604132617</v>
+        <v>3.325326970954375</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-3.062365791830193e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.692548855603923</v>
       </c>
       <c r="JC63" t="n">
-        <v>5.784898025837493</v>
+        <v>3.325321537822907</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC64" t="n">
-        <v>5.784892979216425</v>
+        <v>3.32531649120184</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC65" t="n">
-        <v>5.784893297496642</v>
+        <v>3.325316809482056</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC66" t="n">
-        <v>5.784894388743099</v>
+        <v>3.325317900728513</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC67" t="n">
-        <v>5.784893699135963</v>
+        <v>3.325317211121376</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.368300414422388</v>
+        <v>0.2290082255279058</v>
       </c>
       <c r="JC68" t="n">
-        <v>5.784893729448365</v>
+        <v>3.325317241433779</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-2.134689842160187</v>
+        <v>0.2290082255279058</v>
       </c>
       <c r="JC69" t="n">
-        <v>5.784893539995855</v>
+        <v>3.325317051981268</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.02900822552790575</v>
       </c>
       <c r="JC70" t="n">
-        <v>5.784893593042558</v>
+        <v>3.325317105027972</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.692548855603923</v>
       </c>
       <c r="JC71" t="n">
-        <v>5.784893646089261</v>
+        <v>3.325317158074674</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.368300414422388</v>
+        <v>0.692548855603923</v>
       </c>
       <c r="JC72" t="n">
-        <v>5.784893608198758</v>
+        <v>3.325317120184172</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC73" t="n">
-        <v>5.784893479371052</v>
+        <v>3.325316991356465</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.368300414422388</v>
+        <v>0.2290082255279058</v>
       </c>
       <c r="JC74" t="n">
-        <v>5.784893335387144</v>
+        <v>3.325316847372558</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-2.134689842160187</v>
+        <v>0.02900822552790575</v>
       </c>
       <c r="JC75" t="n">
-        <v>5.784893176247036</v>
+        <v>3.32531668823245</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.02900822552790575</v>
       </c>
       <c r="JC76" t="n">
-        <v>5.784893229293738</v>
+        <v>3.325316741279152</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.692548855603923</v>
       </c>
       <c r="JC77" t="n">
-        <v>5.784893176247036</v>
+        <v>3.32531668823245</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC78" t="n">
-        <v>5.784893176247036</v>
+        <v>3.32531668823245</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC79" t="n">
-        <v>5.784892994372627</v>
+        <v>3.32531650635804</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC80" t="n">
-        <v>5.784893161090835</v>
+        <v>3.325316673076249</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.368300414422388</v>
+        <v>0.2290082255279058</v>
       </c>
       <c r="JC81" t="n">
-        <v>5.784893358121446</v>
+        <v>3.325316870106859</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-2.134689842160187</v>
+        <v>0.02900822552790572</v>
       </c>
       <c r="JC82" t="n">
-        <v>5.784893198981337</v>
+        <v>3.325316710966751</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.02900822552790572</v>
       </c>
       <c r="JC83" t="n">
-        <v>5.784893236871839</v>
+        <v>3.325316748857252</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.692548855603923</v>
       </c>
       <c r="JC84" t="n">
-        <v>5.784893433902449</v>
+        <v>3.325316945887863</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.368300414422388</v>
+        <v>0.02900822552790572</v>
       </c>
       <c r="JC85" t="n">
-        <v>5.784893411168148</v>
+        <v>3.325316923153562</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-2.134689842160187</v>
+        <v>0.02900822552790575</v>
       </c>
       <c r="JC86" t="n">
-        <v>5.78489325960614</v>
+        <v>3.325316771591553</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.02900822552790575</v>
       </c>
       <c r="JC87" t="n">
-        <v>5.784893183825136</v>
+        <v>3.32531669581055</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.692548855603923</v>
       </c>
       <c r="JC88" t="n">
-        <v>5.784893282340442</v>
+        <v>3.325316794325856</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC89" t="n">
-        <v>5.784893289918542</v>
+        <v>3.325316801903956</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.368300414422388</v>
+        <v>0.2290082255279058</v>
       </c>
       <c r="JC90" t="n">
-        <v>5.784893555152056</v>
+        <v>3.325317067137469</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-2.134689842160187</v>
+        <v>0.2290082255279058</v>
       </c>
       <c r="JC91" t="n">
-        <v>5.78489325960614</v>
+        <v>3.325316771591553</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.02900822552790572</v>
       </c>
       <c r="JC92" t="n">
-        <v>5.784893502105352</v>
+        <v>3.325317014090766</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.692548855603923</v>
       </c>
       <c r="JC93" t="n">
-        <v>5.784893585464457</v>
+        <v>3.325317097449871</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC94" t="n">
-        <v>5.784893418746249</v>
+        <v>3.325316930731662</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.368300414422388</v>
+        <v>0.2290082255279058</v>
       </c>
       <c r="JC95" t="n">
-        <v>5.784893608198758</v>
+        <v>3.325317120184172</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.6345324045481114</v>
       </c>
       <c r="JC96" t="n">
-        <v>5.78489325960614</v>
+        <v>3.325316771591553</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-2.134689842160187</v>
+        <v>-0.6345324045481114</v>
       </c>
       <c r="JC97" t="n">
-        <v>5.784893054997429</v>
+        <v>3.325316566982843</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.02900822552790565</v>
       </c>
       <c r="JC98" t="n">
-        <v>5.784893168668935</v>
+        <v>3.325316680654349</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.692548855603923</v>
       </c>
       <c r="JC99" t="n">
-        <v>5.784893183825136</v>
+        <v>3.32531669581055</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC100" t="n">
-        <v>5.784892948904025</v>
+        <v>3.325316460889438</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC101" t="n">
-        <v>5.784893009528827</v>
+        <v>3.325316521514241</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC102" t="n">
-        <v>5.78489288070112</v>
+        <v>3.325316392686534</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.368300414422388</v>
+        <v>0.2290082255279057</v>
       </c>
       <c r="JC103" t="n">
-        <v>5.784893017106928</v>
+        <v>3.325316529092342</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-2.134689842160187</v>
+        <v>0.2290082255279057</v>
       </c>
       <c r="JC104" t="n">
-        <v>5.784893191403237</v>
+        <v>3.32531670338865</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.02900822552790565</v>
       </c>
       <c r="JC105" t="n">
-        <v>5.784893335387144</v>
+        <v>3.325316847372558</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.692548855603923</v>
       </c>
       <c r="JC106" t="n">
-        <v>5.784893168668935</v>
+        <v>3.325316680654349</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC107" t="n">
-        <v>5.784893161090835</v>
+        <v>3.325316673076249</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC108" t="n">
-        <v>5.78489287312302</v>
+        <v>3.325316385108434</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC109" t="n">
-        <v>5.784892888279221</v>
+        <v>3.325316400264635</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC110" t="n">
-        <v>5.784893115622233</v>
+        <v>3.325316627607646</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC111" t="n">
-        <v>5.784893100466031</v>
+        <v>3.325316612451445</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC112" t="n">
-        <v>5.784893206559437</v>
+        <v>3.325316718544851</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.368300414422388</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC113" t="n">
-        <v>5.784892933747823</v>
+        <v>3.325316445733237</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.8925488556039231</v>
       </c>
       <c r="JC114" t="n">
-        <v>5.784893032263128</v>
+        <v>3.325316544248542</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.692548855603923</v>
       </c>
       <c r="JC115" t="n">
-        <v>5.784893183825136</v>
+        <v>3.32531669581055</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.692548855603923</v>
       </c>
       <c r="JC116" t="n">
-        <v>5.784893198981337</v>
+        <v>3.325316710966751</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.692548855603923</v>
       </c>
       <c r="JC117" t="n">
-        <v>5.784893176247036</v>
+        <v>3.32531668823245</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.692548855603923</v>
       </c>
       <c r="JC118" t="n">
-        <v>5.78489325960614</v>
+        <v>3.325316771591553</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.692548855603923</v>
       </c>
       <c r="JC119" t="n">
-        <v>5.784893358121446</v>
+        <v>3.325316870106859</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.692548855603923</v>
       </c>
       <c r="JC120" t="n">
-        <v>5.784893191403237</v>
+        <v>3.32531670338865</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.692548855603923</v>
       </c>
       <c r="JC121" t="n">
-        <v>5.784893176247036</v>
+        <v>3.32531668823245</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.02900822552790565</v>
       </c>
       <c r="JC122" t="n">
-        <v>5.784893145934634</v>
+        <v>3.325316657920048</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-2.134689842160187</v>
+        <v>0.02900822552790565</v>
       </c>
       <c r="JC123" t="n">
-        <v>5.784893130778434</v>
+        <v>3.325316642763847</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.02900822552790565</v>
       </c>
       <c r="JC124" t="n">
-        <v>5.784893168668935</v>
+        <v>3.325316680654349</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7683004144223875</v>
+        <v>0.692548855603923</v>
       </c>
       <c r="JC125" t="n">
-        <v>5.784893183825136</v>
+        <v>3.32531669581055</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.368300414422388</v>
+        <v>0.692548855603923</v>
       </c>
       <c r="JC126" t="n">
-        <v>5.784893176247036</v>
+        <v>3.32531668823245</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_1_000007.xlsx
+++ b/out/Attention-MambaAMT_repeat_1_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.01154759805649519</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.298073034624129</v>
+        <v>-1</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.007876385934650898</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.298073034624129</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.001283994875848293</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6345324045481114</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.03408050164580345</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6345324045481114</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.004773841239511967</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6345324045481114</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.005897757597267628</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.298073034624129</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.008436917327344418</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6345324045481114</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.002139175310730934</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6345324045481114</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.01322775986045599</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6345324045481114</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.006348562426865101</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.098073034624129</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.005901341326534748</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.298073034624129</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.008986194618046284</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.298073034624129</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.008537269197404385</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.298073034624129</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.002293032594025135</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.298073034624129</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.002523014321923256</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.298073034624129</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.01178814005106688</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.298073034624129</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.01275305915623903</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.298073034624129</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.009126133285462856</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.298073034624129</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.008136031217873096</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.298073034624129</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.01779769361019135</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.298073034624129</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.01123697776347399</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.4345324045481114</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.001796843484044075</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.4345324045481114</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.008356715552508831</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.4345324045481114</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.01319186668843031</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.098073034624129</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.0109126390889287</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.098073034624129</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.007318415679037571</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.298073034624129</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.00644993968307972</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.298073034624129</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.01001228298991919</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.298073034624129</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.01086647901684046</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.298073034624129</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.01087314356118441</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.298073034624129</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.01291648391634226</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.298073034624129</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.00391654297709465</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.298073034624129</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.01560730952769518</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.298073034624129</v>
+        <v>0.16</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.01018926966935396</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.4345324045481114</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.01640217378735542</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.2290082255279058</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.02592987939715385</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.2290082255279058</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.01346204336732626</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.2290082255279058</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.002942625433206558</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.2290082255279058</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.000117463736568694</v>
+        <v>-0.0001442297056872631</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.354183399820833</v>
+        <v>1.662755492955732</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.01265568565577269</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.8925488556039231</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>2.710460122790009</v>
+        <v>3.328081305828174</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.2030658415114248</v>
+        <v>0.2493376033478721</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.002097480464726686</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.8925488556039231</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.760590905601549</v>
+        <v>2.161769372984634</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.2538983185004479</v>
+        <v>0.3117531333942921</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.008502747863531113</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.8925488556039231</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
-        <v>2.065354062939217</v>
+        <v>2.535977632975608</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.3639620354825855</v>
+        <v>0.446896638262141</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.02475298196077347</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.8925488556039231</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>2.539523313649628</v>
+        <v>3.118193712197221</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.389367632504495</v>
+        <v>0.4780908817504419</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01878440380096436</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.8925488556039231</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>2.954323354205582</v>
+        <v>3.627512157246003</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4126512097736045</v>
+        <v>0.5066799709751724</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.04087870940566063</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.8925488556039231</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>3.390287604693023</v>
+        <v>4.162817394577987</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1862218161639586</v>
+        <v>0.2286545814118022</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.03964102268218994</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.2290082255279058</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>3.349737115731476</v>
+        <v>4.113026870119093</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.08993598248957481</v>
+        <v>0.110429711811827</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.01483472529798746</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.02900822552790579</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC47" t="n">
-        <v>3.343242528497804</v>
+        <v>4.105052370426346</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.04285243098718765</v>
+        <v>0.05261708287207957</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.04858525469899178</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.6345324045481114</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>3.338938698997445</v>
+        <v>4.099767840511219</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01269539679674733</v>
+        <v>0.01558948000753997</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.03146990761160851</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.02900822552790581</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.321433259006042</v>
+        <v>4.078274628887007</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.008396308371361957</v>
+        <v>0.01031015333330494</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.01337242405861616</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.02900822552790581</v>
+        <v>-0.16</v>
       </c>
       <c r="JC50" t="n">
-        <v>3.325524448542696</v>
+        <v>4.083299178444027</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.004294883863191126</v>
+        <v>0.005274903160156426</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.005354998633265495</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.692548855603923</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>3.325712911363552</v>
+        <v>4.083531734850594</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002194556770350637</v>
+        <v>0.002695874514805839</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.0203818567097187</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.2290082255279059</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>3.325804583164641</v>
+        <v>4.083645439858524</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.000821518329563821</v>
+        <v>0.001009982673942385</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.00155657809227705</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.229008225527906</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>3.32525215400199</v>
+        <v>4.082968241838502</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0004454532635831969</v>
+        <v>0.0005485790107405222</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.001065163873136044</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.0290082255279059</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>3.325321149972224</v>
+        <v>4.083054094460991</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0002119612765024237</v>
+        <v>0.00026123453343704</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.0003823088482022285</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.8925488556039231</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.325299304117223</v>
+        <v>4.083028429691553</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001298018510886005</v>
+        <v>0.0001603044597290868</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.007415829226374626</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.8925488556039231</v>
+        <v>-0.3</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.325346049987977</v>
+        <v>4.083086884481966</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>6.49971027090107e-05</v>
+        <v>8.146700922877794e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.01539355702698231</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.8925488556039231</v>
+        <v>0.3</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.325347194016753</v>
+        <v>4.083089417997475</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.896916644669604e-05</v>
+        <v>3.696191149297746e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.04565737023949623</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.8925488556039231</v>
+        <v>0.3</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.325340061112915</v>
+        <v>4.083081820678642</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.67454884219661e-05</v>
+        <v>2.186207393301694e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.006388514302670956</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.2290082255279059</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.325344848358913</v>
+        <v>4.083088564442286</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>5.490501498730158e-06</v>
+        <v>6.65611277636684e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.01630760729312897</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6345324045481114</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.325337789526157</v>
+        <v>4.083081163178829</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-8.825233700581938e-07</v>
+        <v>1.468457874272584e-07</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.003930514678359032</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6345324045481114</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.325331556863908</v>
+        <v>4.083074656452469</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-2.77474353817759e-06</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.01284866593778133</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.02900822552790579</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.325326970954375</v>
+        <v>4.083070152549514</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.007494147401303053</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.692548855603923</v>
+        <v>-0.3</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.325321537822907</v>
+        <v>4.083064719418045</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.01346977706998587</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.8925488556039231</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.32531649120184</v>
+        <v>4.083059672796978</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.04252344742417336</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.8925488556039231</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.325316809482056</v>
+        <v>4.083059991077194</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.05985182523727417</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.8925488556039231</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.325317900728513</v>
+        <v>4.083061082323651</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.005611076951026917</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.8925488556039231</v>
+        <v>0.16</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.325317211121376</v>
+        <v>4.083060392716515</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.003776788711547852</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.2290082255279058</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.325317241433779</v>
+        <v>4.083060423028917</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.003353608772158623</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.2290082255279058</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.325317051981268</v>
+        <v>4.083060233576407</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>4.566926509141922e-05</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.02900822552790575</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.325317105027972</v>
+        <v>4.08306028662311</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.0008434588089585304</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.692548855603923</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.325317158074674</v>
+        <v>4.083060339669813</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.004880524706095457</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.692548855603923</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.325317120184172</v>
+        <v>4.083060301779311</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.009855251759290695</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.8925488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.325316991356465</v>
+        <v>4.083060172951603</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.004544489551335573</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.2290082255279058</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.325316847372558</v>
+        <v>4.083060028967696</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.002415262162685394</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.02900822552790575</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.32531668823245</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.000662047415971756</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.02900822552790575</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.325316741279152</v>
+        <v>4.08305992287429</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.001051878556609154</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.692548855603923</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.32531668823245</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.0187380351126194</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.8925488556039231</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.32531668823245</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.002879125066101551</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.8925488556039231</v>
+        <v>0.16</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.32531650635804</v>
+        <v>4.083059687953178</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.00459923455491662</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.8925488556039231</v>
+        <v>0.16</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.325316673076249</v>
+        <v>4.083059854671387</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.01283410657197237</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.2290082255279058</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.325316870106859</v>
+        <v>4.083060051701997</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.0006311880424618721</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.02900822552790572</v>
+        <v>0.3</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.325316710966751</v>
+        <v>4.083059892561889</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.01330066472291946</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.02900822552790572</v>
+        <v>0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.325316748857252</v>
+        <v>4.08305993045239</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.01923215016722679</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.692548855603923</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.325316945887863</v>
+        <v>4.083060127483001</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.003323759883642197</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.02900822552790572</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.325316923153562</v>
+        <v>4.0830601047487</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.001359745860099792</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.02900822552790575</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.325316771591553</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.001597086433321238</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.02900822552790575</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.32531669581055</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.009150761179625988</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.692548855603923</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.325316794325856</v>
+        <v>4.083059975920994</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.0135254729539156</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.8925488556039231</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.325316801903956</v>
+        <v>4.083059983499094</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.01544305868446827</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.2290082255279058</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.325317067137469</v>
+        <v>4.083060248732608</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.005508697591722012</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.2290082255279058</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.325316771591553</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.01416115276515484</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.02900822552790572</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.325317014090766</v>
+        <v>4.083060195685905</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.01455126143991947</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.692548855603923</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.325317097449871</v>
+        <v>4.083060279045009</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.03129225224256516</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.8925488556039231</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.325316930731662</v>
+        <v>4.083060112326801</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.01760105043649673</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.2290082255279058</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.325317120184172</v>
+        <v>4.083060301779311</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.005976849235594273</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6345324045481114</v>
+        <v>0.16</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.325316771591553</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.00964376050978899</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6345324045481114</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.325316566982843</v>
+        <v>4.083059748577981</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.004177611321210861</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.02900822552790565</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.325316680654349</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.01845072396099567</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.692548855603923</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.32531669581055</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.002327536232769489</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.8925488556039231</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.325316460889438</v>
+        <v>4.083059642484576</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.007367534097284079</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.8925488556039231</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.325316521514241</v>
+        <v>4.083059703109379</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.0008546747267246246</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.8925488556039231</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.325316392686534</v>
+        <v>4.083059574281672</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.01550679281353951</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.2290082255279057</v>
+        <v>0.3</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.325316529092342</v>
+        <v>4.08305971068748</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.008021962828934193</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.2290082255279057</v>
+        <v>0.16</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.32531670338865</v>
+        <v>4.083059884983788</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.008725512772798538</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.02900822552790565</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.325316847372558</v>
+        <v>4.083060028967696</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.003225207328796387</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.692548855603923</v>
+        <v>0.16</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.325316680654349</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.01423090416938066</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.8925488556039231</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.325316673076249</v>
+        <v>4.083059854671387</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.0006404798477888107</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.8925488556039231</v>
+        <v>0.16</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.325316385108434</v>
+        <v>4.083059566703572</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.000168374739587307</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.8925488556039231</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.325316400264635</v>
+        <v>4.083059581859773</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.01302066445350647</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.8925488556039231</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.325316627607646</v>
+        <v>4.083059809202784</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.005144629161804914</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.8925488556039231</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.325316612451445</v>
+        <v>4.083059794046584</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.008758298121392727</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.8925488556039231</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.325316718544851</v>
+        <v>4.08305990013999</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.002331218682229519</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.8925488556039231</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.325316445733237</v>
+        <v>4.083059627328375</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.001666916534304619</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.8925488556039231</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.325316544248542</v>
+        <v>4.08305972584368</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.003822318278253078</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.692548855603923</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.32531669581055</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.001396307721734047</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.692548855603923</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.325316710966751</v>
+        <v>4.083059892561889</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.002122142817825079</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.692548855603923</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.32531668823245</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.004713741131126881</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.692548855603923</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.325316771591553</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.00225401483476162</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.692548855603923</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.325316870106859</v>
+        <v>4.083060051701997</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.002084607258439064</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.692548855603923</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.32531670338865</v>
+        <v>4.083059884983788</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.001421128399670124</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.692548855603923</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.32531668823245</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.00510117132216692</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.02900822552790565</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.325316657920048</v>
+        <v>4.083059839515186</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.0007607173174619675</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.02900822552790565</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.325316642763847</v>
+        <v>4.083059824358986</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.003204397857189178</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.02900822552790565</v>
+        <v>0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.325316680654349</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.006510491948574781</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.692548855603923</v>
+        <v>0.5800000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.32531669581055</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.006488950923085213</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.692548855603923</v>
+        <v>0.8600000000000003</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.32531668823245</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
   </sheetData>
